--- a/Scripts_annehuitema2003/data_output/GP3_improvements_25-24_sessions/income_ratio_satis_plot/Session_240924/vjcortesa_spendshare_meanplayers_S240924_Round_3_Gall_Pall.xlsx
+++ b/Scripts_annehuitema2003/data_output/GP3_improvements_25-24_sessions/income_ratio_satis_plot/Session_240924/vjcortesa_spendshare_meanplayers_S240924_Round_3_Gall_Pall.xlsx
@@ -530,13 +530,13 @@
         <v>36.281179138322</v>
       </c>
       <c r="F6">
-        <v>3.7</v>
+        <v>3.909090909090909</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>56.62650602409638</v>
+        <v>59.14567360350492</v>
       </c>
     </row>
     <row r="7">
@@ -2153,13 +2153,13 @@
         </is>
       </c>
       <c r="C65">
-        <v>24000</v>
+        <v>96000</v>
       </c>
       <c r="D65">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="E65">
-        <v>27000</v>
+        <v>108000</v>
       </c>
       <c r="F65">
         <v>0.8888888888888888</v>
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>56.62650602409638</v>
+        <v>59.14567360350492</v>
       </c>
       <c r="D6">
-        <v>3.7</v>
+        <v>3.909090909090909</v>
       </c>
     </row>
     <row r="7">
